--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
@@ -413,21 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.14</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.13</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.12</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.11</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.10</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.9</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.8</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.7</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.6</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.5</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.4</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.2</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -438,14 +513,59 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1001</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -456,14 +576,59 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1002</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -474,14 +639,59 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1003</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
@@ -492,14 +702,59 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1004</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
@@ -510,14 +765,59 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1005</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
@@ -413,96 +413,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.19</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.18</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.17</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.16</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.15</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.14</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Unnamed: 0.13</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Unnamed: 0.12</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Unnamed: 0.11</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unnamed: 0.10</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -558,14 +583,29 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>1001</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -621,14 +661,29 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
         <v>1002</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -684,14 +739,29 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
         <v>1003</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
@@ -747,14 +817,29 @@
         <v>3</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
         <v>1004</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
@@ -810,14 +895,29 @@
         <v>4</v>
       </c>
       <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="n">
         <v>1005</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
@@ -413,96 +413,406 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:CC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.76</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.75</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.74</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.73</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.72</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.71</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.70</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.69</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.68</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.67</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.66</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.65</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.64</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.63</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.62</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.61</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.60</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.59</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.58</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.57</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.56</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.55</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.54</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.53</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.52</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.51</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.50</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.49</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.48</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.47</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.46</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.45</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.44</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.43</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.42</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.41</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.40</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.39</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.38</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.37</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.36</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.35</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.34</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.33</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.32</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.31</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.30</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.29</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.28</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.27</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.26</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.25</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.24</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.23</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.22</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.21</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.20</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.19</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.18</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.17</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.16</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.15</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.14</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Unnamed: 0.13</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Unnamed: 0.12</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Unnamed: 0.11</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Unnamed: 0.10</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -558,14 +868,200 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
         <v>1001</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -621,14 +1117,200 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA3" t="n">
         <v>1002</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>Mouse</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
@@ -684,14 +1366,200 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA4" t="n">
         <v>1003</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>Desk</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
@@ -747,14 +1615,200 @@
         <v>3</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="CA5" t="n">
         <v>1004</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>Chair</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>Furniture</t>
         </is>
@@ -810,14 +1864,200 @@
         <v>4</v>
       </c>
       <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="CA6" t="n">
         <v>1005</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>Headphones</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
@@ -1,34 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\Exceltodb-main\Exceltodb-main\OneDrive\Documents\Exceltodb-post_data\Exceltodb-post_data\files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Desk</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Headphones</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +85,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,159 +387,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1001</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>1002</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Mouse</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>1003</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Desk</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>1004</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chair</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1005</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Headphones</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/products.xlsx
@@ -1,72 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\Exceltodb-main\Exceltodb-main\OneDrive\Documents\Exceltodb-post_data\Exceltodb-post_data\files\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
-  <si>
-    <t>product_id</t>
-  </si>
-  <si>
-    <t>product_name</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Electronics</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>Desk</t>
-  </si>
-  <si>
-    <t>Furniture</t>
-  </si>
-  <si>
-    <t>Chair</t>
-  </si>
-  <si>
-    <t>Headphones</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -85,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -387,74 +408,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
+      <c r="B4" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chair</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B6" t="n">
         <v>1005</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Headphones</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
       </c>
     </row>
   </sheetData>
